--- a/Tower_A_Site_Inventory_VedPrakash_Format_v2.xlsx
+++ b/Tower_A_Site_Inventory_VedPrakash_Format_v2.xlsx
@@ -522,13 +522,13 @@
         <v>31000</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="P2">
-        <v>31000</v>
+        <v>27900</v>
       </c>
       <c r="Q2">
-        <v>1116000</v>
+        <v>1004400</v>
       </c>
       <c r="R2" t="str">
         <v>Sold</v>
@@ -634,13 +634,13 @@
         <v>31000</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="P4">
-        <v>31000</v>
+        <v>27900</v>
       </c>
       <c r="Q4">
-        <v>1116000</v>
+        <v>1004400</v>
       </c>
       <c r="R4" t="str">
         <v>Sold</v>
@@ -690,13 +690,13 @@
         <v>31000</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="P5">
-        <v>31000</v>
+        <v>27900</v>
       </c>
       <c r="Q5">
-        <v>1116000</v>
+        <v>1004400</v>
       </c>
       <c r="R5" t="str">
         <v>Sold</v>
@@ -746,13 +746,13 @@
         <v>31000</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="P6">
-        <v>31000</v>
+        <v>27900</v>
       </c>
       <c r="Q6">
-        <v>1116000</v>
+        <v>1004400</v>
       </c>
       <c r="R6" t="str">
         <v>Sold</v>
@@ -1194,13 +1194,13 @@
         <v>31000</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="P14">
-        <v>31000</v>
+        <v>27900</v>
       </c>
       <c r="Q14">
-        <v>2232000</v>
+        <v>2008800</v>
       </c>
       <c r="R14" t="str">
         <v>Sold</v>
@@ -1250,13 +1250,13 @@
         <v>31000</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="P15">
-        <v>31000</v>
+        <v>27900</v>
       </c>
       <c r="Q15">
-        <v>1116000</v>
+        <v>1004400</v>
       </c>
       <c r="R15" t="str">
         <v>Sold</v>
@@ -1362,13 +1362,13 @@
         <v>31000</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="P17">
-        <v>31000</v>
+        <v>27900</v>
       </c>
       <c r="Q17">
-        <v>1116000</v>
+        <v>1004400</v>
       </c>
       <c r="R17" t="str">
         <v>Sold</v>
@@ -1866,13 +1866,13 @@
         <v>31000</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="P26">
-        <v>31000</v>
+        <v>27900</v>
       </c>
       <c r="Q26">
-        <v>1116000</v>
+        <v>1004400</v>
       </c>
       <c r="R26" t="str">
         <v>Sold</v>
@@ -1978,13 +1978,13 @@
         <v>31000</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="P28">
-        <v>31000</v>
+        <v>27900</v>
       </c>
       <c r="Q28">
-        <v>2232000</v>
+        <v>2008800</v>
       </c>
       <c r="R28" t="str">
         <v>Sold</v>
@@ -2034,13 +2034,13 @@
         <v>31000</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="P29">
-        <v>31000</v>
+        <v>27900</v>
       </c>
       <c r="Q29">
-        <v>1116000</v>
+        <v>1004400</v>
       </c>
       <c r="R29" t="str">
         <v>Sold</v>
@@ -2146,13 +2146,13 @@
         <v>31000</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="P31">
-        <v>31000</v>
+        <v>27900</v>
       </c>
       <c r="Q31">
-        <v>1116000</v>
+        <v>1004400</v>
       </c>
       <c r="R31" t="str">
         <v>Sold</v>
@@ -2246,10 +2246,10 @@
         <v>5500000</v>
       </c>
       <c r="K33" t="str">
-        <v/>
+        <v>29/08/2014</v>
       </c>
       <c r="L33" t="str">
-        <v/>
+        <v>10/08/2024</v>
       </c>
       <c r="M33">
         <v>11</v>
@@ -2258,13 +2258,13 @@
         <v>9000</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="P33">
-        <v>9000</v>
+        <v>8100</v>
       </c>
       <c r="Q33">
-        <v>99000</v>
+        <v>89100</v>
       </c>
       <c r="R33" t="str">
         <v>Sold</v>
@@ -2694,10 +2694,10 @@
         <v>5500000</v>
       </c>
       <c r="K41" t="str">
-        <v/>
+        <v>11/11/2014</v>
       </c>
       <c r="L41" t="str">
-        <v/>
+        <v>10/01/2026</v>
       </c>
       <c r="M41">
         <v>36</v>
@@ -3086,10 +3086,10 @@
         <v>5500000</v>
       </c>
       <c r="K48" t="str">
-        <v/>
+        <v>20/11/2014</v>
       </c>
       <c r="L48" t="str">
-        <v/>
+        <v>10/05/2025</v>
       </c>
       <c r="M48">
         <v>36</v>
@@ -3098,13 +3098,13 @@
         <v>11000</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="P48">
-        <v>11000</v>
+        <v>9900</v>
       </c>
       <c r="Q48">
-        <v>396000</v>
+        <v>356400</v>
       </c>
       <c r="R48" t="str">
         <v>Sold</v>
@@ -3478,10 +3478,10 @@
         <v>5500000</v>
       </c>
       <c r="K55" t="str">
-        <v/>
+        <v>30/10/2014</v>
       </c>
       <c r="L55" t="str">
-        <v/>
+        <v>10/05/2025</v>
       </c>
       <c r="M55">
         <v>36</v>
@@ -3490,13 +3490,13 @@
         <v>11000</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="P55">
-        <v>11000</v>
+        <v>9900</v>
       </c>
       <c r="Q55">
-        <v>396000</v>
+        <v>356400</v>
       </c>
       <c r="R55" t="str">
         <v>Sold</v>
@@ -3658,13 +3658,13 @@
         <v>31000</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="P58">
-        <v>31000</v>
+        <v>27900</v>
       </c>
       <c r="Q58">
-        <v>1116000</v>
+        <v>1004400</v>
       </c>
       <c r="R58" t="str">
         <v>Sold</v>
@@ -3702,10 +3702,10 @@
         <v>5500000</v>
       </c>
       <c r="K59" t="str">
-        <v/>
+        <v>28/04/2015</v>
       </c>
       <c r="L59" t="str">
-        <v/>
+        <v>10/05/2025</v>
       </c>
       <c r="M59">
         <v>36</v>
@@ -3714,13 +3714,13 @@
         <v>11000</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="P59">
-        <v>11000</v>
+        <v>9900</v>
       </c>
       <c r="Q59">
-        <v>396000</v>
+        <v>356400</v>
       </c>
       <c r="R59" t="str">
         <v>Sold</v>
@@ -3758,10 +3758,10 @@
         <v>5500000</v>
       </c>
       <c r="K60" t="str">
-        <v/>
+        <v>14/03/2014</v>
       </c>
       <c r="L60" t="str">
-        <v/>
+        <v>10/02/2024</v>
       </c>
       <c r="M60">
         <v>36</v>
@@ -3770,13 +3770,13 @@
         <v>12000</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="P60">
-        <v>12000</v>
+        <v>10800</v>
       </c>
       <c r="Q60">
-        <v>432000</v>
+        <v>388800</v>
       </c>
       <c r="R60" t="str">
         <v>Sold</v>
@@ -4297,7 +4297,7 @@
         <v>4</v>
       </c>
       <c r="D70" t="str">
-        <v>GEETA GIRI</v>
+        <v>Geeta Giri</v>
       </c>
       <c r="E70" t="str">
         <v>+91 9800000413</v>
@@ -4318,25 +4318,25 @@
         <v>5500000</v>
       </c>
       <c r="K70" t="str">
-        <v/>
+        <v>07/07/2014</v>
       </c>
       <c r="L70" t="str">
-        <v/>
+        <v>10/08/2014</v>
       </c>
       <c r="M70">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="N70">
-        <v>31000</v>
+        <v>16000</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="P70">
-        <v>31000</v>
+        <v>14400</v>
       </c>
       <c r="Q70">
-        <v>1116000</v>
+        <v>1440000</v>
       </c>
       <c r="R70" t="str">
         <v>Sold</v>
@@ -4766,25 +4766,25 @@
         <v>5500000</v>
       </c>
       <c r="K78" t="str">
-        <v/>
+        <v>05/07/2014</v>
       </c>
       <c r="L78" t="str">
-        <v/>
+        <v>10/08/2014</v>
       </c>
       <c r="M78">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="N78">
-        <v>31000</v>
+        <v>16000</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="P78">
-        <v>31000</v>
+        <v>14400</v>
       </c>
       <c r="Q78">
-        <v>744000</v>
+        <v>1440000</v>
       </c>
       <c r="R78" t="str">
         <v>Sold</v>
@@ -5046,10 +5046,10 @@
         <v>5500000</v>
       </c>
       <c r="K83" t="str">
-        <v>09/04/1900</v>
+        <v>30/03/2015</v>
       </c>
       <c r="L83" t="str">
-        <v>09/04/1900</v>
+        <v>10/04/2025</v>
       </c>
       <c r="M83">
         <v>24</v>
@@ -5058,13 +5058,13 @@
         <v>11000</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="P83">
-        <v>11000</v>
+        <v>9900</v>
       </c>
       <c r="Q83">
-        <v>264000</v>
+        <v>237600</v>
       </c>
       <c r="R83" t="str">
         <v>Sold</v>
@@ -5830,10 +5830,10 @@
         <v>5500000</v>
       </c>
       <c r="K97" t="str">
-        <v/>
+        <v>15/06/2015</v>
       </c>
       <c r="L97" t="str">
-        <v/>
+        <v>10/06/2025</v>
       </c>
       <c r="M97">
         <v>36</v>
@@ -5886,10 +5886,10 @@
         <v>5500000</v>
       </c>
       <c r="K98" t="str">
-        <v/>
+        <v>31/07/2014</v>
       </c>
       <c r="L98" t="str">
-        <v/>
+        <v>10/07/2024</v>
       </c>
       <c r="M98">
         <v>36</v>
@@ -6682,13 +6682,13 @@
         <v>31000</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="P112">
-        <v>31000</v>
+        <v>27900</v>
       </c>
       <c r="Q112">
-        <v>1116000</v>
+        <v>1004400</v>
       </c>
       <c r="R112" t="str">
         <v>Sold</v>
@@ -7062,10 +7062,10 @@
         <v>5500000</v>
       </c>
       <c r="K119" t="str">
-        <v>09/04/1900</v>
+        <v>15/04/2015</v>
       </c>
       <c r="L119" t="str">
-        <v>09/04/1900</v>
+        <v>10/04/2025</v>
       </c>
       <c r="M119">
         <v>24</v>
@@ -7074,13 +7074,13 @@
         <v>10000</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="P119">
-        <v>10000</v>
+        <v>9000</v>
       </c>
       <c r="Q119">
-        <v>240000</v>
+        <v>216000</v>
       </c>
       <c r="R119" t="str">
         <v>Sold</v>
@@ -7186,13 +7186,13 @@
         <v>31000</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="P121">
-        <v>31000</v>
+        <v>27900</v>
       </c>
       <c r="Q121">
-        <v>1116000</v>
+        <v>1004400</v>
       </c>
       <c r="R121" t="str">
         <v>Sold</v>
@@ -7634,13 +7634,13 @@
         <v>31000</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="P129">
-        <v>31000</v>
+        <v>27900</v>
       </c>
       <c r="Q129">
-        <v>1116000</v>
+        <v>1004400</v>
       </c>
       <c r="R129" t="str">
         <v>Sold</v>
@@ -7846,10 +7846,10 @@
         <v>5500000</v>
       </c>
       <c r="K133" t="str">
-        <v/>
+        <v>17/09/2015</v>
       </c>
       <c r="L133" t="str">
-        <v/>
+        <v>10/11/2023</v>
       </c>
       <c r="M133">
         <v>60</v>
@@ -7858,13 +7858,13 @@
         <v>20972</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>2097.2000000000003</v>
       </c>
       <c r="P133">
-        <v>20972</v>
+        <v>18874.8</v>
       </c>
       <c r="Q133">
-        <v>1258320</v>
+        <v>1132488</v>
       </c>
       <c r="R133" t="str">
         <v>Sold</v>
@@ -8418,13 +8418,13 @@
         <v>31000</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="P143">
-        <v>31000</v>
+        <v>27900</v>
       </c>
       <c r="Q143">
-        <v>1116000</v>
+        <v>1004400</v>
       </c>
       <c r="R143" t="str">
         <v>Sold</v>
@@ -9034,13 +9034,13 @@
         <v>31000</v>
       </c>
       <c r="O154">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="P154">
-        <v>31000</v>
+        <v>27900</v>
       </c>
       <c r="Q154">
-        <v>1116000</v>
+        <v>1004400</v>
       </c>
       <c r="R154" t="str">
         <v>Sold</v>
@@ -9314,13 +9314,13 @@
         <v>21000</v>
       </c>
       <c r="O159">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="P159">
-        <v>21000</v>
+        <v>18900</v>
       </c>
       <c r="Q159">
-        <v>756000</v>
+        <v>680400</v>
       </c>
       <c r="R159" t="str">
         <v>Sold</v>

--- a/Tower_A_Site_Inventory_VedPrakash_Format_v2.xlsx
+++ b/Tower_A_Site_Inventory_VedPrakash_Format_v2.xlsx
@@ -1539,7 +1539,7 @@
         <v>1488000</v>
       </c>
       <c r="R20" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="21">
@@ -2211,7 +2211,7 @@
         <v>1116000</v>
       </c>
       <c r="R32" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="33">
@@ -2267,7 +2267,7 @@
         <v>89100</v>
       </c>
       <c r="R33" t="str">
-        <v>Sold</v>
+        <v>Possession Renewal</v>
       </c>
     </row>
     <row r="34">
@@ -2323,7 +2323,7 @@
         <v>1116000</v>
       </c>
       <c r="R34" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="35">
@@ -2379,7 +2379,7 @@
         <v>1116000</v>
       </c>
       <c r="R35" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="36">
@@ -2715,7 +2715,7 @@
         <v>356400</v>
       </c>
       <c r="R41" t="str">
-        <v>Sold</v>
+        <v>Possession Renewal</v>
       </c>
     </row>
     <row r="42">
@@ -3107,7 +3107,7 @@
         <v>356400</v>
       </c>
       <c r="R48" t="str">
-        <v>Sold</v>
+        <v>Possession Renewal</v>
       </c>
     </row>
     <row r="49">
@@ -3499,7 +3499,7 @@
         <v>356400</v>
       </c>
       <c r="R55" t="str">
-        <v>Sold</v>
+        <v>Possession Renewal</v>
       </c>
     </row>
     <row r="56">
@@ -3611,7 +3611,7 @@
         <v>1116000</v>
       </c>
       <c r="R57" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="58">
@@ -3723,7 +3723,7 @@
         <v>356400</v>
       </c>
       <c r="R59" t="str">
-        <v>Sold</v>
+        <v>Possession Renewal</v>
       </c>
     </row>
     <row r="60">
@@ -3779,7 +3779,7 @@
         <v>388800</v>
       </c>
       <c r="R60" t="str">
-        <v>Sold</v>
+        <v>Possession Renewal</v>
       </c>
     </row>
     <row r="61">
@@ -3835,7 +3835,7 @@
         <v>1116000</v>
       </c>
       <c r="R61" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="62">
@@ -4171,7 +4171,7 @@
         <v>1116000</v>
       </c>
       <c r="R67" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="68">
@@ -4227,7 +4227,7 @@
         <v>1116000</v>
       </c>
       <c r="R68" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="69">
@@ -4339,7 +4339,7 @@
         <v>1440000</v>
       </c>
       <c r="R70" t="str">
-        <v>Sold</v>
+        <v>Possession Renewal</v>
       </c>
     </row>
     <row r="71">
@@ -4451,7 +4451,7 @@
         <v>1116000</v>
       </c>
       <c r="R72" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="73">
@@ -4507,7 +4507,7 @@
         <v>1116000</v>
       </c>
       <c r="R73" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="74">
@@ -4563,7 +4563,7 @@
         <v>1152000</v>
       </c>
       <c r="R74" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="75">
@@ -4787,7 +4787,7 @@
         <v>1440000</v>
       </c>
       <c r="R78" t="str">
-        <v>Sold</v>
+        <v>Possession Renewal</v>
       </c>
     </row>
     <row r="79">
@@ -4843,7 +4843,7 @@
         <v>1116000</v>
       </c>
       <c r="R79" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="80">
@@ -5067,7 +5067,7 @@
         <v>237600</v>
       </c>
       <c r="R83" t="str">
-        <v>Sold</v>
+        <v>Possession Renewal</v>
       </c>
     </row>
     <row r="84">
@@ -5347,7 +5347,7 @@
         <v>1116000</v>
       </c>
       <c r="R88" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="89">
@@ -5515,7 +5515,7 @@
         <v>1116000</v>
       </c>
       <c r="R91" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="92">
@@ -5739,7 +5739,7 @@
         <v>1004400</v>
       </c>
       <c r="R95" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="96">
@@ -5851,7 +5851,7 @@
         <v>356400</v>
       </c>
       <c r="R97" t="str">
-        <v>Sold</v>
+        <v>Possession Renewal</v>
       </c>
     </row>
     <row r="98">
@@ -5907,7 +5907,7 @@
         <v>324000</v>
       </c>
       <c r="R98" t="str">
-        <v>Sold</v>
+        <v>Possession Renewal</v>
       </c>
     </row>
     <row r="99">
@@ -6019,7 +6019,7 @@
         <v>1116000</v>
       </c>
       <c r="R100" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="101">
@@ -6131,7 +6131,7 @@
         <v>1440000</v>
       </c>
       <c r="R102" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="103">
@@ -6299,7 +6299,7 @@
         <v>1116000</v>
       </c>
       <c r="R105" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="106">
@@ -6411,7 +6411,7 @@
         <v>1004400</v>
       </c>
       <c r="R107" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="108">
@@ -6747,7 +6747,7 @@
         <v>1116000</v>
       </c>
       <c r="R113" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="114">
@@ -6803,7 +6803,7 @@
         <v>1260000</v>
       </c>
       <c r="R114" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="115">
@@ -6915,7 +6915,7 @@
         <v>1440000</v>
       </c>
       <c r="R116" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="117">
@@ -7027,7 +7027,7 @@
         <v>1116000</v>
       </c>
       <c r="R118" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="119">
@@ -7083,7 +7083,7 @@
         <v>216000</v>
       </c>
       <c r="R119" t="str">
-        <v>Sold</v>
+        <v>Possession Renewal</v>
       </c>
     </row>
     <row r="120">
@@ -7867,7 +7867,7 @@
         <v>1132488</v>
       </c>
       <c r="R133" t="str">
-        <v>Sold</v>
+        <v>Possession Renewal</v>
       </c>
     </row>
     <row r="134">
@@ -7923,7 +7923,7 @@
         <v>1116000</v>
       </c>
       <c r="R134" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="135">
@@ -8035,7 +8035,7 @@
         <v>104500</v>
       </c>
       <c r="R136" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="137">
@@ -8483,7 +8483,7 @@
         <v>1116000</v>
       </c>
       <c r="R144" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="145">
@@ -8651,7 +8651,7 @@
         <v>1860000</v>
       </c>
       <c r="R147" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="148">
@@ -8763,7 +8763,7 @@
         <v>1116000</v>
       </c>
       <c r="R149" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="150">
@@ -8819,7 +8819,7 @@
         <v>1116000</v>
       </c>
       <c r="R150" t="str">
-        <v>Sold</v>
+        <v>Resell</v>
       </c>
     </row>
     <row r="151">
